--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130246279</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130246322</v>
       </c>
       <c r="B3" t="n">
-        <v>96275</v>
+        <v>96362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130246310</v>
       </c>
       <c r="B4" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,50 +1014,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R5" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,43 +1131,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R6" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1258,7 @@
         <v>130246298</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>130246328</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>130246316</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>130246319</v>
       </c>
       <c r="B10" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>130246313</v>
       </c>
       <c r="B11" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130246324</v>
       </c>
       <c r="B12" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>130246327</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>130246323</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>130246326</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130246287</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>130246311</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>130246289</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246321</v>
+        <v>130246281</v>
       </c>
       <c r="B20" t="n">
-        <v>96179</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,34 +2772,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691604</v>
+        <v>691583</v>
       </c>
       <c r="R20" t="n">
-        <v>6612594</v>
+        <v>6612517</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2840,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2850,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,6 +2859,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2868,43 +2878,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246281</v>
+        <v>130246290</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2912,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691583</v>
+        <v>691639</v>
       </c>
       <c r="R21" t="n">
-        <v>6612517</v>
+        <v>6612574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2974,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,61 +3007,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246290</v>
+        <v>130246333</v>
       </c>
       <c r="B22" t="n">
-        <v>98833</v>
+        <v>58198</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691639</v>
+        <v>691753</v>
       </c>
       <c r="R22" t="n">
-        <v>6612574</v>
+        <v>6612546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3077,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,12 +3087,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3095,7 +3096,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246333</v>
+        <v>130246325</v>
       </c>
       <c r="B23" t="n">
-        <v>58113</v>
+        <v>96266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691753</v>
+        <v>691615</v>
       </c>
       <c r="R23" t="n">
-        <v>6612546</v>
+        <v>6612616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,32 +3221,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246325</v>
+        <v>130246332</v>
       </c>
       <c r="B24" t="n">
-        <v>96179</v>
+        <v>91728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691615</v>
+        <v>691744</v>
       </c>
       <c r="R24" t="n">
-        <v>6612616</v>
+        <v>6612569</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,45 +3328,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130246332</v>
+        <v>130246315</v>
       </c>
       <c r="B25" t="n">
-        <v>91641</v>
+        <v>98920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691744</v>
+        <v>691585</v>
       </c>
       <c r="R25" t="n">
-        <v>6612569</v>
+        <v>6612616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3398,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3424,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3417,6 +3438,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3435,61 +3457,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130246315</v>
+        <v>130246329</v>
       </c>
       <c r="B26" t="n">
-        <v>98833</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691585</v>
+        <v>691752</v>
       </c>
       <c r="R26" t="n">
-        <v>6612616</v>
+        <v>6612571</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,12 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3545,7 +3551,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3564,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130246329</v>
+        <v>130246308</v>
       </c>
       <c r="B27" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3600,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3604,10 +3609,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691752</v>
+        <v>691583</v>
       </c>
       <c r="R27" t="n">
-        <v>6612571</v>
+        <v>6612599</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3639,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3676,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130246280</v>
+        <v>130246286</v>
       </c>
       <c r="B28" t="n">
-        <v>97070</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,34 +3692,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691580</v>
+        <v>691642</v>
       </c>
       <c r="R28" t="n">
-        <v>6612525</v>
+        <v>6612527</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3746,7 +3756,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3756,7 +3766,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,7 +3775,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3784,50 +3793,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130246308</v>
+        <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>57738</v>
+        <v>96266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691583</v>
+        <v>691604</v>
       </c>
       <c r="R29" t="n">
-        <v>6612599</v>
+        <v>6612594</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,7 +3867,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3869,7 +3877,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3878,6 +3886,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3896,50 +3905,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130246286</v>
+        <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>57738</v>
+        <v>98920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691642</v>
+        <v>691849</v>
       </c>
       <c r="R30" t="n">
-        <v>6612527</v>
+        <v>6612693</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,19 +3985,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:18</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 st bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,21 +4001,2367 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130270392</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>691647</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6612527</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>22 st bladrosetter 1 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130270402</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>691834</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6612675</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>4 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130270409</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>691818</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6612608</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>20 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130270397</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>691797</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6612650</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>11 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130270401</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>691833</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6612667</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>23 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130270384</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>691742</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6612548</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130270403</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>691844</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6612687</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>25 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130270404</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>691845</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6612692</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>19 st bladrosetter, 1 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130270400</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>691817</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6612668</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>56 st bladrosetter 2 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130270386</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>691797</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6612651</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Övriga läten</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130270387</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58198</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>691658</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6612525</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4 födsökande</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130270393</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>691643</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6612531</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>54 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130270385</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>691724</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6612579</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130270413</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>691796</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6612568</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130270412</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>691796</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6612574</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>35 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130270405</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>691844</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6612691</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130270410</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>691817</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6612612</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>10 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130270391</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>691649</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6612519</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>5 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130270417</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>691737</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6612549</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130270390</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>691652</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6612519</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>16 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130270411</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>691810</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6612613</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>5 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -6135,7 +6135,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B50" t="n">
         <v>98920</v>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R50" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,7 +6250,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270411</v>
+        <v>130270390</v>
       </c>
       <c r="B51" t="n">
         <v>98920</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691810</v>
+        <v>691652</v>
       </c>
       <c r="R51" t="n">
-        <v>6612613</v>
+        <v>6612519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>5 st bladrosetter</t>
+          <t>16 st bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -6135,7 +6135,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270411</v>
+        <v>130270390</v>
       </c>
       <c r="B50" t="n">
         <v>98920</v>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691810</v>
+        <v>691652</v>
       </c>
       <c r="R50" t="n">
-        <v>6612613</v>
+        <v>6612519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>5 st bladrosetter</t>
+          <t>16 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,7 +6250,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B51" t="n">
         <v>98920</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R51" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246328</v>
+        <v>130246316</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,34 +1390,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691768</v>
+        <v>691591</v>
       </c>
       <c r="R8" t="n">
-        <v>6612575</v>
+        <v>6612610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246316</v>
+        <v>130246319</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,39 +1502,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691591</v>
+        <v>691599</v>
       </c>
       <c r="R9" t="n">
-        <v>6612610</v>
+        <v>6612602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,7 +1598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246319</v>
+        <v>130246328</v>
       </c>
       <c r="B10" t="n">
         <v>91728</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691599</v>
+        <v>691768</v>
       </c>
       <c r="R10" t="n">
-        <v>6612602</v>
+        <v>6612575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1919,61 +1919,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R13" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,7 +2013,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2043,50 +2031,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R14" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,6 +2136,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246281</v>
+        <v>130246333</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>58198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,43 +2772,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691583</v>
+        <v>691753</v>
       </c>
       <c r="R20" t="n">
-        <v>6612517</v>
+        <v>6612546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,7 +2850,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2878,61 +2868,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246290</v>
+        <v>130246325</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>96266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691639</v>
+        <v>691615</v>
       </c>
       <c r="R21" t="n">
-        <v>6612574</v>
+        <v>6612616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,12 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,7 +2957,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3007,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246333</v>
+        <v>130246281</v>
       </c>
       <c r="B22" t="n">
-        <v>58198</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3018,34 +2986,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691753</v>
+        <v>691583</v>
       </c>
       <c r="R22" t="n">
-        <v>6612546</v>
+        <v>6612517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3087,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,6 +3073,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3114,32 +3092,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246325</v>
+        <v>130246332</v>
       </c>
       <c r="B23" t="n">
-        <v>96266</v>
+        <v>91728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3149,10 +3127,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691615</v>
+        <v>691744</v>
       </c>
       <c r="R23" t="n">
-        <v>6612616</v>
+        <v>6612569</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,45 +3199,61 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246332</v>
+        <v>130246290</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>98920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691744</v>
+        <v>691639</v>
       </c>
       <c r="R24" t="n">
-        <v>6612569</v>
+        <v>6612574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3295,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,6 +3309,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3328,61 +3328,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130246315</v>
+        <v>130246329</v>
       </c>
       <c r="B25" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691585</v>
+        <v>691752</v>
       </c>
       <c r="R25" t="n">
-        <v>6612616</v>
+        <v>6612571</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,7 +3403,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3424,12 +3413,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,7 +3422,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3457,50 +3440,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130246329</v>
+        <v>130246315</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691752</v>
+        <v>691585</v>
       </c>
       <c r="R26" t="n">
-        <v>6612571</v>
+        <v>6612616</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3532,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3536,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,6 +3550,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -5042,27 +5042,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130270386</v>
+        <v>130270387</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>58198</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691797</v>
+        <v>691658</v>
       </c>
       <c r="R40" t="n">
-        <v>6612651</v>
+        <v>6612525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Övriga läten</t>
+          <t>4 födsökande</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,27 +5144,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130270387</v>
+        <v>130270386</v>
       </c>
       <c r="B41" t="n">
-        <v>58198</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691658</v>
+        <v>691797</v>
       </c>
       <c r="R41" t="n">
-        <v>6612525</v>
+        <v>6612651</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>4 födsökande</t>
+          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5246,7 +5246,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130270393</v>
+        <v>130270413</v>
       </c>
       <c r="B42" t="n">
         <v>98920</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691643</v>
+        <v>691796</v>
       </c>
       <c r="R42" t="n">
-        <v>6612531</v>
+        <v>6612568</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>10 st bladrosetter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5361,45 +5361,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130270385</v>
+        <v>130270412</v>
       </c>
       <c r="B43" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691724</v>
+        <v>691796</v>
       </c>
       <c r="R43" t="n">
-        <v>6612579</v>
+        <v>6612574</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5436,7 +5448,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>35 st bladrosetter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5445,6 +5457,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5463,7 +5476,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130270413</v>
+        <v>130270405</v>
       </c>
       <c r="B44" t="n">
         <v>98920</v>
@@ -5493,7 +5506,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5510,10 +5523,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691796</v>
+        <v>691844</v>
       </c>
       <c r="R44" t="n">
-        <v>6612568</v>
+        <v>6612691</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5550,7 +5563,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>10 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,7 +5591,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270412</v>
+        <v>130270393</v>
       </c>
       <c r="B45" t="n">
         <v>98920</v>
@@ -5608,7 +5621,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5625,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691796</v>
+        <v>691643</v>
       </c>
       <c r="R45" t="n">
-        <v>6612574</v>
+        <v>6612531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5678,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>35 st bladrosetter</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,57 +5706,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270405</v>
+        <v>130270385</v>
       </c>
       <c r="B46" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691844</v>
+        <v>691724</v>
       </c>
       <c r="R46" t="n">
-        <v>6612691</v>
+        <v>6612579</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5781,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5789,7 +5790,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246316</v>
+        <v>130246328</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,39 +1390,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691591</v>
+        <v>691768</v>
       </c>
       <c r="R8" t="n">
-        <v>6612610</v>
+        <v>6612575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246328</v>
+        <v>130246316</v>
       </c>
       <c r="B10" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,34 +1604,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691768</v>
+        <v>691591</v>
       </c>
       <c r="R10" t="n">
-        <v>6612575</v>
+        <v>6612610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1919,50 +1919,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R13" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,6 +2024,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2031,61 +2043,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R14" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2137,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2761,32 +2761,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246333</v>
+        <v>130246332</v>
       </c>
       <c r="B20" t="n">
-        <v>58198</v>
+        <v>91728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691753</v>
+        <v>691744</v>
       </c>
       <c r="R20" t="n">
-        <v>6612546</v>
+        <v>6612569</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3092,45 +3092,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246332</v>
+        <v>130246290</v>
       </c>
       <c r="B23" t="n">
-        <v>91728</v>
+        <v>98920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691744</v>
+        <v>691639</v>
       </c>
       <c r="R23" t="n">
-        <v>6612569</v>
+        <v>6612574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3172,7 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,6 +3202,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3199,61 +3221,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246290</v>
+        <v>130246333</v>
       </c>
       <c r="B24" t="n">
-        <v>98920</v>
+        <v>58198</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691639</v>
+        <v>691753</v>
       </c>
       <c r="R24" t="n">
-        <v>6612574</v>
+        <v>6612546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,12 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,7 +3310,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3328,50 +3328,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130246329</v>
+        <v>130246315</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691752</v>
+        <v>691585</v>
       </c>
       <c r="R25" t="n">
-        <v>6612571</v>
+        <v>6612616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3424,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,6 +3438,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3440,61 +3457,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130246315</v>
+        <v>130246329</v>
       </c>
       <c r="B26" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691585</v>
+        <v>691752</v>
       </c>
       <c r="R26" t="n">
-        <v>6612616</v>
+        <v>6612571</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3526,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,12 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,7 +3551,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -5042,27 +5042,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130270387</v>
+        <v>130270386</v>
       </c>
       <c r="B40" t="n">
-        <v>58198</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691658</v>
+        <v>691797</v>
       </c>
       <c r="R40" t="n">
-        <v>6612525</v>
+        <v>6612651</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>4 födsökande</t>
+          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,27 +5144,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130270386</v>
+        <v>130270387</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>58198</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691797</v>
+        <v>691658</v>
       </c>
       <c r="R41" t="n">
-        <v>6612651</v>
+        <v>6612525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Övriga läten</t>
+          <t>4 födsökande</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5246,57 +5246,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130270413</v>
+        <v>130270385</v>
       </c>
       <c r="B42" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691796</v>
+        <v>691724</v>
       </c>
       <c r="R42" t="n">
-        <v>6612568</v>
+        <v>6612579</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5333,7 +5321,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10 st bladrosetter</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5342,7 +5330,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5361,7 +5348,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130270412</v>
+        <v>130270413</v>
       </c>
       <c r="B43" t="n">
         <v>98920</v>
@@ -5391,7 +5378,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5411,7 +5398,7 @@
         <v>691796</v>
       </c>
       <c r="R43" t="n">
-        <v>6612574</v>
+        <v>6612568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5448,7 +5435,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>35 st bladrosetter</t>
+          <t>10 st bladrosetter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5476,7 +5463,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130270405</v>
+        <v>130270412</v>
       </c>
       <c r="B44" t="n">
         <v>98920</v>
@@ -5506,7 +5493,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5523,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691844</v>
+        <v>691796</v>
       </c>
       <c r="R44" t="n">
-        <v>6612691</v>
+        <v>6612574</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5563,7 +5550,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>35 st bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5591,7 +5578,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270393</v>
+        <v>130270405</v>
       </c>
       <c r="B45" t="n">
         <v>98920</v>
@@ -5621,7 +5608,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5638,10 +5625,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691643</v>
+        <v>691844</v>
       </c>
       <c r="R45" t="n">
-        <v>6612531</v>
+        <v>6612691</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5678,7 +5665,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5706,45 +5693,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270385</v>
+        <v>130270393</v>
       </c>
       <c r="B46" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691724</v>
+        <v>691643</v>
       </c>
       <c r="R46" t="n">
-        <v>6612579</v>
+        <v>6612531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5781,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5790,6 +5789,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6038,45 +6038,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270417</v>
+        <v>130270390</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691737</v>
+        <v>691652</v>
       </c>
       <c r="R49" t="n">
-        <v>6612549</v>
+        <v>6612519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6111,12 +6123,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>16 st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6135,7 +6153,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B50" t="n">
         <v>98920</v>
@@ -6165,7 +6183,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6182,10 +6200,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R50" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,7 +6240,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,57 +6268,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270411</v>
+        <v>130270417</v>
       </c>
       <c r="B51" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691810</v>
+        <v>691737</v>
       </c>
       <c r="R51" t="n">
-        <v>6612613</v>
+        <v>6612549</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6335,18 +6341,12 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>5 st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1014,43 +1014,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R5" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,50 +1138,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R6" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,61 +1255,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246298</v>
+        <v>130246319</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691628</v>
+        <v>691599</v>
       </c>
       <c r="R7" t="n">
-        <v>6612648</v>
+        <v>6612602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1344,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1486,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246319</v>
+        <v>130246316</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691599</v>
+        <v>691591</v>
       </c>
       <c r="R9" t="n">
-        <v>6612602</v>
+        <v>6612610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,50 +1581,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246316</v>
+        <v>130246298</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691591</v>
+        <v>691628</v>
       </c>
       <c r="R10" t="n">
-        <v>6612610</v>
+        <v>6612648</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,6 +1686,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2761,32 +2761,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246332</v>
+        <v>130246333</v>
       </c>
       <c r="B20" t="n">
-        <v>91728</v>
+        <v>58198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691744</v>
+        <v>691753</v>
       </c>
       <c r="R20" t="n">
-        <v>6612569</v>
+        <v>6612546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,32 +2868,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246325</v>
+        <v>130246332</v>
       </c>
       <c r="B21" t="n">
-        <v>96266</v>
+        <v>91728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691615</v>
+        <v>691744</v>
       </c>
       <c r="R21" t="n">
-        <v>6612616</v>
+        <v>6612569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246281</v>
+        <v>130246325</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>96266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2986,43 +2986,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691583</v>
+        <v>691615</v>
       </c>
       <c r="R22" t="n">
-        <v>6612517</v>
+        <v>6612616</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3045,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3055,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,7 +3064,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3092,50 +3082,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246290</v>
+        <v>130246281</v>
       </c>
       <c r="B23" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3143,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691639</v>
+        <v>691583</v>
       </c>
       <c r="R23" t="n">
-        <v>6612574</v>
+        <v>6612517</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,12 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,45 +3199,61 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246333</v>
+        <v>130246290</v>
       </c>
       <c r="B24" t="n">
-        <v>58198</v>
+        <v>98920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691753</v>
+        <v>691639</v>
       </c>
       <c r="R24" t="n">
-        <v>6612546</v>
+        <v>6612574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3295,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,6 +3309,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -6038,57 +6038,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270390</v>
+        <v>130270417</v>
       </c>
       <c r="B49" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691652</v>
+        <v>691737</v>
       </c>
       <c r="R49" t="n">
-        <v>6612519</v>
+        <v>6612549</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6123,18 +6111,12 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>16 st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6153,7 +6135,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270411</v>
+        <v>130270390</v>
       </c>
       <c r="B50" t="n">
         <v>98920</v>
@@ -6183,7 +6165,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6200,10 +6182,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691810</v>
+        <v>691652</v>
       </c>
       <c r="R50" t="n">
-        <v>6612613</v>
+        <v>6612519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6240,7 +6222,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>5 st bladrosetter</t>
+          <t>16 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6268,45 +6250,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270417</v>
+        <v>130270411</v>
       </c>
       <c r="B51" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691737</v>
+        <v>691810</v>
       </c>
       <c r="R51" t="n">
-        <v>6612549</v>
+        <v>6612613</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6341,12 +6335,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>5 st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1014,43 +1014,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R5" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,50 +1138,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R6" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2761,43 +2761,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246281</v>
+        <v>130246290</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2805,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691583</v>
+        <v>691639</v>
       </c>
       <c r="R20" t="n">
-        <v>6612517</v>
+        <v>6612574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,7 +2857,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2878,61 +2890,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246290</v>
+        <v>130246332</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>91728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691639</v>
+        <v>691744</v>
       </c>
       <c r="R21" t="n">
-        <v>6612574</v>
+        <v>6612569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2960,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,12 +2970,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,7 +2979,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3007,10 +2997,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246333</v>
+        <v>130246281</v>
       </c>
       <c r="B22" t="n">
-        <v>58198</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3018,34 +3008,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691753</v>
+        <v>691583</v>
       </c>
       <c r="R22" t="n">
-        <v>6612546</v>
+        <v>6612517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,7 +3076,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3087,7 +3086,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,6 +3095,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3114,32 +3114,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246332</v>
+        <v>130246325</v>
       </c>
       <c r="B23" t="n">
-        <v>91728</v>
+        <v>96266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691744</v>
+        <v>691615</v>
       </c>
       <c r="R23" t="n">
-        <v>6612569</v>
+        <v>6612616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246325</v>
+        <v>130246333</v>
       </c>
       <c r="B24" t="n">
-        <v>96266</v>
+        <v>58198</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691615</v>
+        <v>691753</v>
       </c>
       <c r="R24" t="n">
-        <v>6612616</v>
+        <v>6612546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270411</v>
+        <v>130270390</v>
       </c>
       <c r="B50" t="n">
         <v>98920</v>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691810</v>
+        <v>691652</v>
       </c>
       <c r="R50" t="n">
-        <v>6612613</v>
+        <v>6612519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>5 st bladrosetter</t>
+          <t>16 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,7 +6250,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B51" t="n">
         <v>98920</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R51" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1014,50 +1014,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R5" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,43 +1131,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R6" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2890,32 +2890,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246332</v>
+        <v>130246325</v>
       </c>
       <c r="B21" t="n">
-        <v>91728</v>
+        <v>96266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691744</v>
+        <v>691615</v>
       </c>
       <c r="R21" t="n">
-        <v>6612569</v>
+        <v>6612616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2997,54 +2997,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246281</v>
+        <v>130246332</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>91728</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691583</v>
+        <v>691744</v>
       </c>
       <c r="R22" t="n">
-        <v>6612517</v>
+        <v>6612569</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3076,7 +3067,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3086,7 +3077,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3095,7 +3086,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3114,10 +3104,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246325</v>
+        <v>130246281</v>
       </c>
       <c r="B23" t="n">
-        <v>96266</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,34 +3115,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691615</v>
+        <v>691583</v>
       </c>
       <c r="R23" t="n">
-        <v>6612616</v>
+        <v>6612517</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,6 +3202,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1014,43 +1014,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R5" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,50 +1138,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R6" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2761,50 +2761,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246290</v>
+        <v>130246281</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2812,10 +2805,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691639</v>
+        <v>691583</v>
       </c>
       <c r="R20" t="n">
-        <v>6612574</v>
+        <v>6612517</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2847,7 +2840,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,12 +2850,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,45 +2878,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246325</v>
+        <v>130246290</v>
       </c>
       <c r="B21" t="n">
-        <v>96266</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691615</v>
+        <v>691639</v>
       </c>
       <c r="R21" t="n">
-        <v>6612616</v>
+        <v>6612574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2970,7 +2974,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,6 +2988,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2997,32 +3007,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246332</v>
+        <v>130246333</v>
       </c>
       <c r="B22" t="n">
-        <v>91728</v>
+        <v>58198</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3032,10 +3042,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691744</v>
+        <v>691753</v>
       </c>
       <c r="R22" t="n">
-        <v>6612569</v>
+        <v>6612546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3067,7 +3077,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3077,7 +3087,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3104,54 +3114,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246281</v>
+        <v>130246332</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>91728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691583</v>
+        <v>691744</v>
       </c>
       <c r="R23" t="n">
-        <v>6612517</v>
+        <v>6612569</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,7 +3203,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246333</v>
+        <v>130246325</v>
       </c>
       <c r="B24" t="n">
-        <v>58198</v>
+        <v>96266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691753</v>
+        <v>691615</v>
       </c>
       <c r="R24" t="n">
-        <v>6612546</v>
+        <v>6612616</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B50" t="n">
         <v>98920</v>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R50" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,7 +6250,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270411</v>
+        <v>130270390</v>
       </c>
       <c r="B51" t="n">
         <v>98920</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691810</v>
+        <v>691652</v>
       </c>
       <c r="R51" t="n">
-        <v>6612613</v>
+        <v>6612519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>5 st bladrosetter</t>
+          <t>16 st bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130246322</v>
       </c>
       <c r="B3" t="n">
-        <v>96362</v>
+        <v>96365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130246310</v>
       </c>
       <c r="B4" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,50 +1014,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R5" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,43 +1131,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R6" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246328</v>
+        <v>130246316</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691768</v>
+        <v>691591</v>
       </c>
       <c r="R7" t="n">
-        <v>6612575</v>
+        <v>6612610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,45 +1367,61 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246319</v>
+        <v>130246298</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691599</v>
+        <v>691628</v>
       </c>
       <c r="R8" t="n">
-        <v>6612602</v>
+        <v>6612648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1472,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246316</v>
+        <v>130246328</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>91731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,39 +1502,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691591</v>
+        <v>691768</v>
       </c>
       <c r="R9" t="n">
-        <v>6612610</v>
+        <v>6612575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,61 +1598,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246298</v>
+        <v>130246319</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>91731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691628</v>
+        <v>691599</v>
       </c>
       <c r="R10" t="n">
-        <v>6612648</v>
+        <v>6612602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1687,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>130246324</v>
       </c>
       <c r="B12" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,61 +1919,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R13" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,7 +2013,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2043,50 +2031,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R14" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,6 +2136,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>130246287</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>130246311</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>130246289</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,54 +2761,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246281</v>
+        <v>130246332</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>91731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691583</v>
+        <v>691744</v>
       </c>
       <c r="R20" t="n">
-        <v>6612517</v>
+        <v>6612569</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,7 +2850,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2878,61 +2868,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246290</v>
+        <v>130246325</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>96269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691639</v>
+        <v>691615</v>
       </c>
       <c r="R21" t="n">
-        <v>6612574</v>
+        <v>6612616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,12 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,7 +2957,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3007,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246333</v>
+        <v>130246281</v>
       </c>
       <c r="B22" t="n">
-        <v>58198</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3018,34 +2986,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691753</v>
+        <v>691583</v>
       </c>
       <c r="R22" t="n">
-        <v>6612546</v>
+        <v>6612517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3087,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,6 +3073,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3114,32 +3092,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246332</v>
+        <v>130246333</v>
       </c>
       <c r="B23" t="n">
-        <v>91728</v>
+        <v>58198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3149,10 +3127,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691744</v>
+        <v>691753</v>
       </c>
       <c r="R23" t="n">
-        <v>6612569</v>
+        <v>6612546</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,45 +3199,61 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246325</v>
+        <v>130246290</v>
       </c>
       <c r="B24" t="n">
-        <v>96266</v>
+        <v>98923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691615</v>
+        <v>691639</v>
       </c>
       <c r="R24" t="n">
-        <v>6612616</v>
+        <v>6612574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3295,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,6 +3309,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3328,50 +3328,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130246329</v>
+        <v>130246315</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>98923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691752</v>
+        <v>691585</v>
       </c>
       <c r="R25" t="n">
-        <v>6612571</v>
+        <v>6612616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3424,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,6 +3438,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3440,61 +3457,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130246315</v>
+        <v>130246329</v>
       </c>
       <c r="B26" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691585</v>
+        <v>691752</v>
       </c>
       <c r="R26" t="n">
-        <v>6612616</v>
+        <v>6612571</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3526,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,12 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,7 +3551,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>96266</v>
+        <v>96269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>130270392</v>
       </c>
       <c r="B31" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130270402</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130270409</v>
       </c>
       <c r="B33" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>130270397</v>
       </c>
       <c r="B34" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>130270401</v>
       </c>
       <c r="B35" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130270403</v>
       </c>
       <c r="B37" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>130270404</v>
       </c>
       <c r="B38" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>130270400</v>
       </c>
       <c r="B39" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130270413</v>
       </c>
       <c r="B43" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>130270412</v>
       </c>
       <c r="B44" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>130270405</v>
       </c>
       <c r="B45" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>130270393</v>
       </c>
       <c r="B46" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>130270410</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>130270391</v>
       </c>
       <c r="B48" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6038,45 +6038,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270417</v>
+        <v>130270390</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>98923</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691737</v>
+        <v>691652</v>
       </c>
       <c r="R49" t="n">
-        <v>6612549</v>
+        <v>6612519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6111,12 +6123,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>16 st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6138,7 +6156,7 @@
         <v>130270411</v>
       </c>
       <c r="B50" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,57 +6268,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270390</v>
+        <v>130270417</v>
       </c>
       <c r="B51" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691652</v>
+        <v>691737</v>
       </c>
       <c r="R51" t="n">
-        <v>6612519</v>
+        <v>6612549</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6335,18 +6341,12 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>16 st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246279</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130246322</v>
       </c>
       <c r="B3" t="n">
-        <v>96365</v>
+        <v>96391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130246310</v>
       </c>
       <c r="B4" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>130246307</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,50 +1255,61 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246316</v>
+        <v>130246298</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691591</v>
+        <v>691628</v>
       </c>
       <c r="R7" t="n">
-        <v>6612610</v>
+        <v>6612648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,6 +1360,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,61 +1379,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246298</v>
+        <v>130246328</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>91757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691628</v>
+        <v>691768</v>
       </c>
       <c r="R8" t="n">
-        <v>6612648</v>
+        <v>6612575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1468,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246328</v>
+        <v>130246319</v>
       </c>
       <c r="B9" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691768</v>
+        <v>691599</v>
       </c>
       <c r="R9" t="n">
-        <v>6612575</v>
+        <v>6612602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246319</v>
+        <v>130246316</v>
       </c>
       <c r="B10" t="n">
-        <v>91731</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,34 +1604,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691599</v>
+        <v>691591</v>
       </c>
       <c r="R10" t="n">
-        <v>6612602</v>
+        <v>6612610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,7 +1708,7 @@
         <v>130246313</v>
       </c>
       <c r="B11" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130246324</v>
       </c>
       <c r="B12" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,50 +1919,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R13" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,6 +2024,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2031,61 +2043,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R14" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2137,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>130246326</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130246287</v>
+        <v>130246311</v>
       </c>
       <c r="B17" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691641</v>
+        <v>691587</v>
       </c>
       <c r="R17" t="n">
-        <v>6612561</v>
+        <v>6612603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2480,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130246311</v>
+        <v>130246287</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2543,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2548,7 +2553,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691587</v>
+        <v>691641</v>
       </c>
       <c r="R18" t="n">
-        <v>6612603</v>
+        <v>6612561</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,12 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,7 +2640,7 @@
         <v>130246289</v>
       </c>
       <c r="B19" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,32 +2761,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246332</v>
+        <v>130246333</v>
       </c>
       <c r="B20" t="n">
-        <v>91731</v>
+        <v>58224</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691744</v>
+        <v>691753</v>
       </c>
       <c r="R20" t="n">
-        <v>6612569</v>
+        <v>6612546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246325</v>
+        <v>130246281</v>
       </c>
       <c r="B21" t="n">
-        <v>96269</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,34 +2879,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691615</v>
+        <v>691583</v>
       </c>
       <c r="R21" t="n">
-        <v>6612616</v>
+        <v>6612517</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,6 +2966,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2975,43 +2985,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246281</v>
+        <v>130246290</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3019,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691583</v>
+        <v>691639</v>
       </c>
       <c r="R22" t="n">
-        <v>6612517</v>
+        <v>6612574</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3081,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,32 +3114,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246333</v>
+        <v>130246332</v>
       </c>
       <c r="B23" t="n">
-        <v>58198</v>
+        <v>91757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3127,10 +3149,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691753</v>
+        <v>691744</v>
       </c>
       <c r="R23" t="n">
-        <v>6612546</v>
+        <v>6612569</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3172,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,61 +3221,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246290</v>
+        <v>130246325</v>
       </c>
       <c r="B24" t="n">
-        <v>98923</v>
+        <v>96295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691639</v>
+        <v>691615</v>
       </c>
       <c r="R24" t="n">
-        <v>6612574</v>
+        <v>6612616</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,12 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,7 +3310,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3328,61 +3328,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130246315</v>
+        <v>130246329</v>
       </c>
       <c r="B25" t="n">
-        <v>98923</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691585</v>
+        <v>691752</v>
       </c>
       <c r="R25" t="n">
-        <v>6612616</v>
+        <v>6612571</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,7 +3403,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3424,12 +3413,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,7 +3422,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3457,50 +3440,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130246329</v>
+        <v>130246315</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>98949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691752</v>
+        <v>691585</v>
       </c>
       <c r="R26" t="n">
-        <v>6612571</v>
+        <v>6612616</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3532,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3536,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,6 +3550,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>130246308</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>130246286</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>96269</v>
+        <v>96295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>130270392</v>
       </c>
       <c r="B31" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130270402</v>
       </c>
       <c r="B32" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130270409</v>
       </c>
       <c r="B33" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>130270397</v>
       </c>
       <c r="B34" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>130270401</v>
       </c>
       <c r="B35" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>130270384</v>
       </c>
       <c r="B36" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130270403</v>
       </c>
       <c r="B37" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>130270404</v>
       </c>
       <c r="B38" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>130270400</v>
       </c>
       <c r="B39" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,27 +5042,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130270386</v>
+        <v>130270387</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>58224</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691797</v>
+        <v>691658</v>
       </c>
       <c r="R40" t="n">
-        <v>6612651</v>
+        <v>6612525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Övriga läten</t>
+          <t>4 födsökande</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,27 +5144,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130270387</v>
+        <v>130270386</v>
       </c>
       <c r="B41" t="n">
-        <v>58198</v>
+        <v>57849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691658</v>
+        <v>691797</v>
       </c>
       <c r="R41" t="n">
-        <v>6612525</v>
+        <v>6612651</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>4 födsökande</t>
+          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5249,7 +5249,7 @@
         <v>130270385</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130270413</v>
       </c>
       <c r="B43" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>130270412</v>
       </c>
       <c r="B44" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>130270405</v>
       </c>
       <c r="B45" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>130270393</v>
       </c>
       <c r="B46" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>130270410</v>
       </c>
       <c r="B47" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>130270391</v>
       </c>
       <c r="B48" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>130270390</v>
       </c>
       <c r="B49" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>130270411</v>
       </c>
       <c r="B50" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1014,43 +1014,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R5" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,50 +1138,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R6" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2384,7 +2384,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130246311</v>
+        <v>130246287</v>
       </c>
       <c r="B17" t="n">
         <v>98949</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691587</v>
+        <v>691641</v>
       </c>
       <c r="R17" t="n">
-        <v>6612603</v>
+        <v>6612561</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,12 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,7 +2508,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130246287</v>
+        <v>130246311</v>
       </c>
       <c r="B18" t="n">
         <v>98949</v>
@@ -2543,7 +2538,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2553,7 +2548,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2564,10 +2559,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691641</v>
+        <v>691587</v>
       </c>
       <c r="R18" t="n">
-        <v>6612561</v>
+        <v>6612603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,7 +2604,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5042,27 +5042,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130270387</v>
+        <v>130270386</v>
       </c>
       <c r="B40" t="n">
-        <v>58224</v>
+        <v>57849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691658</v>
+        <v>691797</v>
       </c>
       <c r="R40" t="n">
-        <v>6612525</v>
+        <v>6612651</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>4 födsökande</t>
+          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,27 +5144,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130270386</v>
+        <v>130270387</v>
       </c>
       <c r="B41" t="n">
-        <v>57849</v>
+        <v>58224</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691797</v>
+        <v>691658</v>
       </c>
       <c r="R41" t="n">
-        <v>6612651</v>
+        <v>6612525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Övriga läten</t>
+          <t>4 födsökande</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5578,7 +5578,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270405</v>
+        <v>130270393</v>
       </c>
       <c r="B45" t="n">
         <v>98949</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691844</v>
+        <v>691643</v>
       </c>
       <c r="R45" t="n">
-        <v>6612691</v>
+        <v>6612531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,7 +5693,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270393</v>
+        <v>130270405</v>
       </c>
       <c r="B46" t="n">
         <v>98949</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691643</v>
+        <v>691844</v>
       </c>
       <c r="R46" t="n">
-        <v>6612531</v>
+        <v>6612691</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130246322</v>
       </c>
       <c r="B3" t="n">
-        <v>96391</v>
+        <v>96392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130246310</v>
       </c>
       <c r="B4" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>130246307</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>130246298</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246328</v>
+        <v>130246319</v>
       </c>
       <c r="B8" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691768</v>
+        <v>691599</v>
       </c>
       <c r="R8" t="n">
-        <v>6612575</v>
+        <v>6612602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246319</v>
+        <v>130246328</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691599</v>
+        <v>691768</v>
       </c>
       <c r="R9" t="n">
-        <v>6612602</v>
+        <v>6612575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1815,7 +1815,7 @@
         <v>130246324</v>
       </c>
       <c r="B12" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,61 +1919,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R13" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,7 +2013,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2043,50 +2031,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R14" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,6 +2136,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>130246287</v>
       </c>
       <c r="B17" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>130246311</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>130246289</v>
       </c>
       <c r="B19" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,32 +2761,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246333</v>
+        <v>130246332</v>
       </c>
       <c r="B20" t="n">
-        <v>58224</v>
+        <v>91758</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691753</v>
+        <v>691744</v>
       </c>
       <c r="R20" t="n">
-        <v>6612546</v>
+        <v>6612569</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246281</v>
+        <v>130246325</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>96296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,43 +2879,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691583</v>
+        <v>691615</v>
       </c>
       <c r="R21" t="n">
-        <v>6612517</v>
+        <v>6612616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,7 +2957,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2988,7 +2978,7 @@
         <v>130246290</v>
       </c>
       <c r="B22" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,45 +3104,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246332</v>
+        <v>130246281</v>
       </c>
       <c r="B23" t="n">
-        <v>91757</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691744</v>
+        <v>691583</v>
       </c>
       <c r="R23" t="n">
-        <v>6612569</v>
+        <v>6612517</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,6 +3202,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246325</v>
+        <v>130246333</v>
       </c>
       <c r="B24" t="n">
-        <v>96295</v>
+        <v>58224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691615</v>
+        <v>691753</v>
       </c>
       <c r="R24" t="n">
-        <v>6612616</v>
+        <v>6612546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3443,7 +3443,7 @@
         <v>130246315</v>
       </c>
       <c r="B26" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>96295</v>
+        <v>96296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>130270392</v>
       </c>
       <c r="B31" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130270402</v>
       </c>
       <c r="B32" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130270409</v>
       </c>
       <c r="B33" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>130270397</v>
       </c>
       <c r="B34" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>130270401</v>
       </c>
       <c r="B35" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130270403</v>
       </c>
       <c r="B37" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>130270404</v>
       </c>
       <c r="B38" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>130270400</v>
       </c>
       <c r="B39" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130270413</v>
       </c>
       <c r="B43" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130270412</v>
+        <v>130270405</v>
       </c>
       <c r="B44" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691796</v>
+        <v>691844</v>
       </c>
       <c r="R44" t="n">
-        <v>6612574</v>
+        <v>6612691</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>35 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,10 +5578,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270393</v>
+        <v>130270412</v>
       </c>
       <c r="B45" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691643</v>
+        <v>691796</v>
       </c>
       <c r="R45" t="n">
-        <v>6612531</v>
+        <v>6612574</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>35 st bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270405</v>
+        <v>130270393</v>
       </c>
       <c r="B46" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691844</v>
+        <v>691643</v>
       </c>
       <c r="R46" t="n">
-        <v>6612691</v>
+        <v>6612531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5811,7 +5811,7 @@
         <v>130270410</v>
       </c>
       <c r="B47" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>130270391</v>
       </c>
       <c r="B48" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B49" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R49" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6153,10 +6153,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270411</v>
+        <v>130270390</v>
       </c>
       <c r="B50" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691810</v>
+        <v>691652</v>
       </c>
       <c r="R50" t="n">
-        <v>6612613</v>
+        <v>6612519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>5 st bladrosetter</t>
+          <t>16 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130246322</v>
       </c>
       <c r="B3" t="n">
-        <v>96392</v>
+        <v>96393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130246310</v>
       </c>
       <c r="B4" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,50 +1014,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R5" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,43 +1131,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R6" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,61 +1255,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246298</v>
+        <v>130246319</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>91759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691628</v>
+        <v>691599</v>
       </c>
       <c r="R7" t="n">
-        <v>6612648</v>
+        <v>6612602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1344,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1379,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246319</v>
+        <v>130246328</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1414,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691599</v>
+        <v>691768</v>
       </c>
       <c r="R8" t="n">
-        <v>6612602</v>
+        <v>6612575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246328</v>
+        <v>130246316</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691768</v>
+        <v>691591</v>
       </c>
       <c r="R9" t="n">
-        <v>6612575</v>
+        <v>6612610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,50 +1581,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246316</v>
+        <v>130246298</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691591</v>
+        <v>691628</v>
       </c>
       <c r="R10" t="n">
-        <v>6612610</v>
+        <v>6612648</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,6 +1686,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>130246324</v>
       </c>
       <c r="B12" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>130246327</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130246287</v>
       </c>
       <c r="B17" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>130246311</v>
       </c>
       <c r="B18" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>130246289</v>
       </c>
       <c r="B19" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>130246332</v>
       </c>
       <c r="B20" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>130246325</v>
       </c>
       <c r="B21" t="n">
-        <v>96296</v>
+        <v>96297</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,61 +2975,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246290</v>
+        <v>130246333</v>
       </c>
       <c r="B22" t="n">
-        <v>98950</v>
+        <v>58224</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691639</v>
+        <v>691753</v>
       </c>
       <c r="R22" t="n">
-        <v>6612574</v>
+        <v>6612546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3045,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,12 +3055,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,7 +3064,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3104,43 +3082,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246281</v>
+        <v>130246290</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>98951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3148,10 +3133,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691583</v>
+        <v>691639</v>
       </c>
       <c r="R23" t="n">
-        <v>6612517</v>
+        <v>6612574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3178,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246333</v>
+        <v>130246281</v>
       </c>
       <c r="B24" t="n">
-        <v>58224</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,34 +3222,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691753</v>
+        <v>691583</v>
       </c>
       <c r="R24" t="n">
-        <v>6612546</v>
+        <v>6612517</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3290,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3300,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,6 +3309,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>130246315</v>
       </c>
       <c r="B26" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>96296</v>
+        <v>96297</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>130270392</v>
       </c>
       <c r="B31" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130270402</v>
       </c>
       <c r="B32" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130270409</v>
       </c>
       <c r="B33" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>130270397</v>
       </c>
       <c r="B34" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>130270401</v>
       </c>
       <c r="B35" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130270403</v>
       </c>
       <c r="B37" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>130270404</v>
       </c>
       <c r="B38" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>130270400</v>
       </c>
       <c r="B39" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130270413</v>
       </c>
       <c r="B43" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130270405</v>
+        <v>130270412</v>
       </c>
       <c r="B44" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691844</v>
+        <v>691796</v>
       </c>
       <c r="R44" t="n">
-        <v>6612691</v>
+        <v>6612574</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>35 st bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,10 +5578,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270412</v>
+        <v>130270393</v>
       </c>
       <c r="B45" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691796</v>
+        <v>691643</v>
       </c>
       <c r="R45" t="n">
-        <v>6612574</v>
+        <v>6612531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>35 st bladrosetter</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270393</v>
+        <v>130270405</v>
       </c>
       <c r="B46" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691643</v>
+        <v>691844</v>
       </c>
       <c r="R46" t="n">
-        <v>6612531</v>
+        <v>6612691</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5811,7 +5811,7 @@
         <v>130270410</v>
       </c>
       <c r="B47" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>130270391</v>
       </c>
       <c r="B48" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6038,57 +6038,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270411</v>
+        <v>130270417</v>
       </c>
       <c r="B49" t="n">
-        <v>98950</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691810</v>
+        <v>691737</v>
       </c>
       <c r="R49" t="n">
-        <v>6612613</v>
+        <v>6612549</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6123,18 +6111,12 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>5 st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6156,7 +6138,7 @@
         <v>130270390</v>
       </c>
       <c r="B50" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6268,45 +6250,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270417</v>
+        <v>130270411</v>
       </c>
       <c r="B51" t="n">
-        <v>5177</v>
+        <v>98951</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691737</v>
+        <v>691810</v>
       </c>
       <c r="R51" t="n">
-        <v>6612549</v>
+        <v>6612613</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6341,12 +6335,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>5 st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246279</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130246322</v>
       </c>
       <c r="B3" t="n">
-        <v>96393</v>
+        <v>96395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130246310</v>
       </c>
       <c r="B4" t="n">
-        <v>106018</v>
+        <v>106020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>130246307</v>
       </c>
       <c r="B6" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246319</v>
+        <v>130246316</v>
       </c>
       <c r="B7" t="n">
-        <v>91759</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691599</v>
+        <v>691591</v>
       </c>
       <c r="R7" t="n">
-        <v>6612602</v>
+        <v>6612610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,45 +1367,61 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246328</v>
+        <v>130246298</v>
       </c>
       <c r="B8" t="n">
-        <v>91759</v>
+        <v>98953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691768</v>
+        <v>691628</v>
       </c>
       <c r="R8" t="n">
-        <v>6612575</v>
+        <v>6612648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1472,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246316</v>
+        <v>130246328</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>91761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,39 +1502,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691591</v>
+        <v>691768</v>
       </c>
       <c r="R9" t="n">
-        <v>6612610</v>
+        <v>6612575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,61 +1598,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246298</v>
+        <v>130246319</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>91761</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691628</v>
+        <v>691599</v>
       </c>
       <c r="R10" t="n">
-        <v>6612648</v>
+        <v>6612602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1687,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>130246313</v>
       </c>
       <c r="B11" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130246324</v>
       </c>
       <c r="B12" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,50 +1919,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>98953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R13" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,6 +2024,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2031,61 +2043,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B14" t="n">
-        <v>98951</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R14" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2137,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>130246326</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130246287</v>
       </c>
       <c r="B17" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>130246311</v>
       </c>
       <c r="B18" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>130246289</v>
       </c>
       <c r="B19" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,32 +2761,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246332</v>
+        <v>130246333</v>
       </c>
       <c r="B20" t="n">
-        <v>91759</v>
+        <v>58226</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691744</v>
+        <v>691753</v>
       </c>
       <c r="R20" t="n">
-        <v>6612569</v>
+        <v>6612546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,45 +2868,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246325</v>
+        <v>130246290</v>
       </c>
       <c r="B21" t="n">
-        <v>96297</v>
+        <v>98953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691615</v>
+        <v>691639</v>
       </c>
       <c r="R21" t="n">
-        <v>6612616</v>
+        <v>6612574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2964,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,6 +2978,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2975,32 +2997,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246333</v>
+        <v>130246332</v>
       </c>
       <c r="B22" t="n">
-        <v>58224</v>
+        <v>91761</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3010,10 +3032,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691753</v>
+        <v>691744</v>
       </c>
       <c r="R22" t="n">
-        <v>6612546</v>
+        <v>6612569</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,7 +3067,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3055,7 +3077,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,61 +3104,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246290</v>
+        <v>130246325</v>
       </c>
       <c r="B23" t="n">
-        <v>98951</v>
+        <v>96299</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691639</v>
+        <v>691615</v>
       </c>
       <c r="R23" t="n">
-        <v>6612574</v>
+        <v>6612616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,12 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,7 +3193,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>130246329</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>130246315</v>
       </c>
       <c r="B26" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>130246308</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>130246286</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>96297</v>
+        <v>96299</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>130270392</v>
       </c>
       <c r="B31" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130270402</v>
       </c>
       <c r="B32" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130270409</v>
       </c>
       <c r="B33" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>130270397</v>
       </c>
       <c r="B34" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>130270401</v>
       </c>
       <c r="B35" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>130270384</v>
       </c>
       <c r="B36" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130270403</v>
       </c>
       <c r="B37" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>130270404</v>
       </c>
       <c r="B38" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>130270400</v>
       </c>
       <c r="B39" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>130270386</v>
       </c>
       <c r="B40" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>130270387</v>
       </c>
       <c r="B41" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>130270385</v>
       </c>
       <c r="B42" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130270413</v>
       </c>
       <c r="B43" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>130270412</v>
       </c>
       <c r="B44" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270393</v>
+        <v>130270405</v>
       </c>
       <c r="B45" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691643</v>
+        <v>691844</v>
       </c>
       <c r="R45" t="n">
-        <v>6612531</v>
+        <v>6612691</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270405</v>
+        <v>130270393</v>
       </c>
       <c r="B46" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691844</v>
+        <v>691643</v>
       </c>
       <c r="R46" t="n">
-        <v>6612691</v>
+        <v>6612531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5811,7 +5811,7 @@
         <v>130270410</v>
       </c>
       <c r="B47" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>130270391</v>
       </c>
       <c r="B48" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6038,45 +6038,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270417</v>
+        <v>130270390</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>98953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691737</v>
+        <v>691652</v>
       </c>
       <c r="R49" t="n">
-        <v>6612549</v>
+        <v>6612519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6111,12 +6123,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>16 st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6135,10 +6153,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B50" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6183,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6182,10 +6200,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R50" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,7 +6240,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,57 +6268,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270411</v>
+        <v>130270417</v>
       </c>
       <c r="B51" t="n">
-        <v>98951</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691810</v>
+        <v>691737</v>
       </c>
       <c r="R51" t="n">
-        <v>6612613</v>
+        <v>6612549</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6335,18 +6341,12 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>5 st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130246322</v>
       </c>
       <c r="B3" t="n">
-        <v>96395</v>
+        <v>96399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130246310</v>
       </c>
       <c r="B4" t="n">
-        <v>106020</v>
+        <v>106024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,43 +1014,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R5" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,50 +1138,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B6" t="n">
-        <v>98953</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R6" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246316</v>
+        <v>130246319</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691591</v>
+        <v>691599</v>
       </c>
       <c r="R7" t="n">
-        <v>6612610</v>
+        <v>6612602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,61 +1362,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246298</v>
+        <v>130246328</v>
       </c>
       <c r="B8" t="n">
-        <v>98953</v>
+        <v>91761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691628</v>
+        <v>691768</v>
       </c>
       <c r="R8" t="n">
-        <v>6612648</v>
+        <v>6612575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1451,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,45 +1469,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246328</v>
+        <v>130246298</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691768</v>
+        <v>691628</v>
       </c>
       <c r="R9" t="n">
-        <v>6612575</v>
+        <v>6612648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,6 +1574,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246319</v>
+        <v>130246316</v>
       </c>
       <c r="B10" t="n">
-        <v>91761</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,34 +1604,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691599</v>
+        <v>691591</v>
       </c>
       <c r="R10" t="n">
-        <v>6612602</v>
+        <v>6612610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1922,7 +1922,7 @@
         <v>130246327</v>
       </c>
       <c r="B13" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,27 +2155,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130246326</v>
+        <v>130246284</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>5197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2184,21 +2184,25 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691614</v>
+        <v>691642</v>
       </c>
       <c r="R15" t="n">
-        <v>6612631</v>
+        <v>6612527</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,6 +2253,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2267,27 +2272,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130246284</v>
+        <v>130246326</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2296,25 +2301,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691642</v>
+        <v>691614</v>
       </c>
       <c r="R16" t="n">
-        <v>6612527</v>
+        <v>6612631</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2357,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2366,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>130246287</v>
       </c>
       <c r="B17" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>130246311</v>
       </c>
       <c r="B18" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>130246289</v>
       </c>
       <c r="B19" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246333</v>
+        <v>130246325</v>
       </c>
       <c r="B20" t="n">
-        <v>58226</v>
+        <v>96303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,21 +2772,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691753</v>
+        <v>691615</v>
       </c>
       <c r="R20" t="n">
-        <v>6612546</v>
+        <v>6612616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,61 +2868,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246290</v>
+        <v>130246332</v>
       </c>
       <c r="B21" t="n">
-        <v>98953</v>
+        <v>91761</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691639</v>
+        <v>691744</v>
       </c>
       <c r="R21" t="n">
-        <v>6612574</v>
+        <v>6612569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,12 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,7 +2957,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2997,45 +2975,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246332</v>
+        <v>130246281</v>
       </c>
       <c r="B22" t="n">
-        <v>91761</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691744</v>
+        <v>691583</v>
       </c>
       <c r="R22" t="n">
-        <v>6612569</v>
+        <v>6612517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3067,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3077,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,6 +3073,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3104,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246325</v>
+        <v>130246333</v>
       </c>
       <c r="B23" t="n">
-        <v>96299</v>
+        <v>58226</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,21 +3103,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2818</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3139,10 +3127,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691615</v>
+        <v>691753</v>
       </c>
       <c r="R23" t="n">
-        <v>6612616</v>
+        <v>6612546</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,43 +3199,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246281</v>
+        <v>130246290</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>98957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3255,10 +3250,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691583</v>
+        <v>691639</v>
       </c>
       <c r="R24" t="n">
-        <v>6612517</v>
+        <v>6612574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3290,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3300,7 +3295,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3443,7 +3443,7 @@
         <v>130246315</v>
       </c>
       <c r="B26" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>96299</v>
+        <v>96303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>130270392</v>
       </c>
       <c r="B31" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130270402</v>
       </c>
       <c r="B32" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130270409</v>
       </c>
       <c r="B33" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>130270397</v>
       </c>
       <c r="B34" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>130270401</v>
       </c>
       <c r="B35" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130270403</v>
       </c>
       <c r="B37" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>130270404</v>
       </c>
       <c r="B38" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>130270400</v>
       </c>
       <c r="B39" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130270413</v>
       </c>
       <c r="B43" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>130270412</v>
       </c>
       <c r="B44" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>130270405</v>
       </c>
       <c r="B45" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>130270393</v>
       </c>
       <c r="B46" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>130270410</v>
       </c>
       <c r="B47" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>130270391</v>
       </c>
       <c r="B48" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6038,57 +6038,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270390</v>
+        <v>130270417</v>
       </c>
       <c r="B49" t="n">
-        <v>98953</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691652</v>
+        <v>691737</v>
       </c>
       <c r="R49" t="n">
-        <v>6612519</v>
+        <v>6612549</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6123,18 +6111,12 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>16 st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6153,10 +6135,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270411</v>
+        <v>130270390</v>
       </c>
       <c r="B50" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6165,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6200,10 +6182,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691810</v>
+        <v>691652</v>
       </c>
       <c r="R50" t="n">
-        <v>6612613</v>
+        <v>6612519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6240,7 +6222,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>5 st bladrosetter</t>
+          <t>16 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6268,45 +6250,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270417</v>
+        <v>130270411</v>
       </c>
       <c r="B51" t="n">
-        <v>5177</v>
+        <v>98957</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691737</v>
+        <v>691810</v>
       </c>
       <c r="R51" t="n">
-        <v>6612549</v>
+        <v>6612613</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6341,12 +6335,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>5 st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1014,50 +1014,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R5" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,43 +1131,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R6" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246319</v>
+        <v>130246316</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691599</v>
+        <v>691591</v>
       </c>
       <c r="R7" t="n">
-        <v>6612602</v>
+        <v>6612610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,45 +1367,61 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246328</v>
+        <v>130246298</v>
       </c>
       <c r="B8" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691768</v>
+        <v>691628</v>
       </c>
       <c r="R8" t="n">
-        <v>6612575</v>
+        <v>6612648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1472,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,61 +1491,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246298</v>
+        <v>130246328</v>
       </c>
       <c r="B9" t="n">
-        <v>98957</v>
+        <v>91761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691628</v>
+        <v>691768</v>
       </c>
       <c r="R9" t="n">
-        <v>6612648</v>
+        <v>6612575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1580,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246316</v>
+        <v>130246319</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,39 +1609,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691591</v>
+        <v>691599</v>
       </c>
       <c r="R10" t="n">
-        <v>6612610</v>
+        <v>6612602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1919,61 +1919,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B13" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R13" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,7 +2013,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2043,50 +2031,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B14" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R14" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,6 +2136,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,27 +2155,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130246284</v>
+        <v>130246326</v>
       </c>
       <c r="B15" t="n">
-        <v>5197</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2184,25 +2184,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691642</v>
+        <v>691614</v>
       </c>
       <c r="R15" t="n">
-        <v>6612527</v>
+        <v>6612631</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2240,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,7 +2249,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2272,27 +2267,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130246326</v>
+        <v>130246284</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2301,21 +2296,25 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691614</v>
+        <v>691642</v>
       </c>
       <c r="R16" t="n">
-        <v>6612631</v>
+        <v>6612527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,6 +2365,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3328,50 +3328,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130246329</v>
+        <v>130246315</v>
       </c>
       <c r="B25" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691752</v>
+        <v>691585</v>
       </c>
       <c r="R25" t="n">
-        <v>6612571</v>
+        <v>6612616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3424,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,6 +3438,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3440,61 +3457,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130246315</v>
+        <v>130246329</v>
       </c>
       <c r="B26" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691585</v>
+        <v>691752</v>
       </c>
       <c r="R26" t="n">
-        <v>6612616</v>
+        <v>6612571</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3526,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,12 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,7 +3551,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130270397</v>
+        <v>130270401</v>
       </c>
       <c r="B34" t="n">
         <v>98957</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691797</v>
+        <v>691833</v>
       </c>
       <c r="R34" t="n">
-        <v>6612650</v>
+        <v>6612667</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>11 st bladrosetter</t>
+          <t>23 st bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4480,7 +4480,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130270401</v>
+        <v>130270397</v>
       </c>
       <c r="B35" t="n">
         <v>98957</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691833</v>
+        <v>691797</v>
       </c>
       <c r="R35" t="n">
-        <v>6612667</v>
+        <v>6612650</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>23 st bladrosetter</t>
+          <t>11 st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5463,7 +5463,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130270412</v>
+        <v>130270405</v>
       </c>
       <c r="B44" t="n">
         <v>98957</v>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691796</v>
+        <v>691844</v>
       </c>
       <c r="R44" t="n">
-        <v>6612574</v>
+        <v>6612691</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>35 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,7 +5578,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270405</v>
+        <v>130270393</v>
       </c>
       <c r="B45" t="n">
         <v>98957</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691844</v>
+        <v>691643</v>
       </c>
       <c r="R45" t="n">
-        <v>6612691</v>
+        <v>6612531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,7 +5693,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270393</v>
+        <v>130270412</v>
       </c>
       <c r="B46" t="n">
         <v>98957</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691643</v>
+        <v>691796</v>
       </c>
       <c r="R46" t="n">
-        <v>6612531</v>
+        <v>6612574</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>35 st bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1014,43 +1014,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130246331</v>
+        <v>130246307</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691743</v>
+        <v>691584</v>
       </c>
       <c r="R5" t="n">
-        <v>6612571</v>
+        <v>6612585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,50 +1138,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130246307</v>
+        <v>130246331</v>
       </c>
       <c r="B6" t="n">
-        <v>98957</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691584</v>
+        <v>691743</v>
       </c>
       <c r="R6" t="n">
-        <v>6612585</v>
+        <v>6612571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246316</v>
+        <v>130246319</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691591</v>
+        <v>691599</v>
       </c>
       <c r="R7" t="n">
-        <v>6612610</v>
+        <v>6612602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,61 +1362,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246298</v>
+        <v>130246328</v>
       </c>
       <c r="B8" t="n">
-        <v>98957</v>
+        <v>91761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691628</v>
+        <v>691768</v>
       </c>
       <c r="R8" t="n">
-        <v>6612648</v>
+        <v>6612575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1451,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130246328</v>
+        <v>130246316</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691768</v>
+        <v>691591</v>
       </c>
       <c r="R9" t="n">
-        <v>6612575</v>
+        <v>6612610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,45 +1581,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130246319</v>
+        <v>130246298</v>
       </c>
       <c r="B10" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691599</v>
+        <v>691628</v>
       </c>
       <c r="R10" t="n">
-        <v>6612602</v>
+        <v>6612648</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,6 +1686,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2761,32 +2761,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130246325</v>
+        <v>130246332</v>
       </c>
       <c r="B20" t="n">
-        <v>96303</v>
+        <v>91761</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691615</v>
+        <v>691744</v>
       </c>
       <c r="R20" t="n">
-        <v>6612616</v>
+        <v>6612569</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,32 +2868,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246332</v>
+        <v>130246325</v>
       </c>
       <c r="B21" t="n">
-        <v>91761</v>
+        <v>96303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691744</v>
+        <v>691615</v>
       </c>
       <c r="R21" t="n">
-        <v>6612569</v>
+        <v>6612616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4365,7 +4365,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130270401</v>
+        <v>130270397</v>
       </c>
       <c r="B34" t="n">
         <v>98957</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691833</v>
+        <v>691797</v>
       </c>
       <c r="R34" t="n">
-        <v>6612667</v>
+        <v>6612650</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>23 st bladrosetter</t>
+          <t>11 st bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4480,7 +4480,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130270397</v>
+        <v>130270401</v>
       </c>
       <c r="B35" t="n">
         <v>98957</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691797</v>
+        <v>691833</v>
       </c>
       <c r="R35" t="n">
-        <v>6612650</v>
+        <v>6612667</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>11 st bladrosetter</t>
+          <t>23 st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5246,45 +5246,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130270385</v>
+        <v>130270412</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691724</v>
+        <v>691796</v>
       </c>
       <c r="R42" t="n">
-        <v>6612579</v>
+        <v>6612574</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5321,7 +5333,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>35 st bladrosetter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,6 +5342,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5348,7 +5361,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130270413</v>
+        <v>130270405</v>
       </c>
       <c r="B43" t="n">
         <v>98957</v>
@@ -5378,7 +5391,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5395,10 +5408,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691796</v>
+        <v>691844</v>
       </c>
       <c r="R43" t="n">
-        <v>6612568</v>
+        <v>6612691</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5435,7 +5448,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10 st bladrosetter</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5463,7 +5476,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130270405</v>
+        <v>130270393</v>
       </c>
       <c r="B44" t="n">
         <v>98957</v>
@@ -5493,7 +5506,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5510,10 +5523,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691844</v>
+        <v>691643</v>
       </c>
       <c r="R44" t="n">
-        <v>6612691</v>
+        <v>6612531</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5550,7 +5563,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,57 +5591,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270393</v>
+        <v>130270385</v>
       </c>
       <c r="B45" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691643</v>
+        <v>691724</v>
       </c>
       <c r="R45" t="n">
-        <v>6612531</v>
+        <v>6612579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5666,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5674,7 +5675,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270412</v>
+        <v>130270413</v>
       </c>
       <c r="B46" t="n">
         <v>98957</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5743,7 +5743,7 @@
         <v>691796</v>
       </c>
       <c r="R46" t="n">
-        <v>6612574</v>
+        <v>6612568</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>35 st bladrosetter</t>
+          <t>10 st bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130246319</v>
+        <v>130246328</v>
       </c>
       <c r="B7" t="n">
         <v>91761</v>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691599</v>
+        <v>691768</v>
       </c>
       <c r="R7" t="n">
-        <v>6612602</v>
+        <v>6612575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130246328</v>
+        <v>130246319</v>
       </c>
       <c r="B8" t="n">
         <v>91761</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691768</v>
+        <v>691599</v>
       </c>
       <c r="R8" t="n">
-        <v>6612575</v>
+        <v>6612602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1919,50 +1919,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130246323</v>
+        <v>130246327</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691593</v>
+        <v>691771</v>
       </c>
       <c r="R13" t="n">
-        <v>6612591</v>
+        <v>6612575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,6 +2024,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2031,61 +2043,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130246327</v>
+        <v>130246323</v>
       </c>
       <c r="B14" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691771</v>
+        <v>691593</v>
       </c>
       <c r="R14" t="n">
-        <v>6612575</v>
+        <v>6612591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2137,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,27 +2155,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130246326</v>
+        <v>130246284</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>5197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2184,21 +2184,25 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691614</v>
+        <v>691642</v>
       </c>
       <c r="R15" t="n">
-        <v>6612631</v>
+        <v>6612527</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,6 +2253,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2267,27 +2272,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130246284</v>
+        <v>130246326</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2296,25 +2301,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691642</v>
+        <v>691614</v>
       </c>
       <c r="R16" t="n">
-        <v>6612527</v>
+        <v>6612631</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2357,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2366,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130246325</v>
+        <v>130246281</v>
       </c>
       <c r="B21" t="n">
-        <v>96303</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,34 +2879,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691615</v>
+        <v>691583</v>
       </c>
       <c r="R21" t="n">
-        <v>6612616</v>
+        <v>6612517</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,6 +2966,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2975,43 +2985,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130246281</v>
+        <v>130246290</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3019,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691583</v>
+        <v>691639</v>
       </c>
       <c r="R22" t="n">
-        <v>6612517</v>
+        <v>6612574</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3081,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,10 +3114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130246333</v>
+        <v>130246325</v>
       </c>
       <c r="B23" t="n">
-        <v>58226</v>
+        <v>96303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3103,21 +3125,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3127,10 +3149,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691753</v>
+        <v>691615</v>
       </c>
       <c r="R23" t="n">
-        <v>6612546</v>
+        <v>6612616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3172,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,61 +3221,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130246290</v>
+        <v>130246333</v>
       </c>
       <c r="B24" t="n">
-        <v>98957</v>
+        <v>58226</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691639</v>
+        <v>691753</v>
       </c>
       <c r="R24" t="n">
-        <v>6612574</v>
+        <v>6612546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,12 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,7 +3310,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3328,61 +3328,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130246315</v>
+        <v>130246329</v>
       </c>
       <c r="B25" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691585</v>
+        <v>691752</v>
       </c>
       <c r="R25" t="n">
-        <v>6612616</v>
+        <v>6612571</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,7 +3403,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3424,12 +3413,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,7 +3422,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3457,50 +3440,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130246329</v>
+        <v>130246315</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691752</v>
+        <v>691585</v>
       </c>
       <c r="R26" t="n">
-        <v>6612571</v>
+        <v>6612616</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3532,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3536,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,6 +3550,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5246,57 +5246,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130270412</v>
+        <v>130270385</v>
       </c>
       <c r="B42" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691796</v>
+        <v>691724</v>
       </c>
       <c r="R42" t="n">
-        <v>6612574</v>
+        <v>6612579</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5333,7 +5321,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>35 st bladrosetter</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5342,7 +5330,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5361,7 +5348,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130270405</v>
+        <v>130270413</v>
       </c>
       <c r="B43" t="n">
         <v>98957</v>
@@ -5391,7 +5378,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5408,10 +5395,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691844</v>
+        <v>691796</v>
       </c>
       <c r="R43" t="n">
-        <v>6612691</v>
+        <v>6612568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5448,7 +5435,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>34 st bladrosetter och 4 vinterståndare</t>
+          <t>10 st bladrosetter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,14 +5456,14 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130270393</v>
+        <v>130270412</v>
       </c>
       <c r="B44" t="n">
         <v>98957</v>
@@ -5506,7 +5493,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5523,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691643</v>
+        <v>691796</v>
       </c>
       <c r="R44" t="n">
-        <v>6612531</v>
+        <v>6612574</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5563,7 +5550,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>54 st bladrosetter</t>
+          <t>35 st bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5584,52 +5571,64 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130270385</v>
+        <v>130270405</v>
       </c>
       <c r="B45" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691724</v>
+        <v>691844</v>
       </c>
       <c r="R45" t="n">
-        <v>6612579</v>
+        <v>6612691</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5666,7 +5665,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>34 st bladrosetter och 4 vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5675,6 +5674,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130270413</v>
+        <v>130270393</v>
       </c>
       <c r="B46" t="n">
         <v>98957</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691796</v>
+        <v>691643</v>
       </c>
       <c r="R46" t="n">
-        <v>6612568</v>
+        <v>6612531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>10 st bladrosetter</t>
+          <t>54 st bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>130246321</v>
       </c>
       <c r="B29" t="n">
-        <v>96303</v>
+        <v>96316</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>130270406</v>
       </c>
       <c r="B30" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>130270392</v>
       </c>
       <c r="B31" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130270402</v>
       </c>
       <c r="B32" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130270409</v>
       </c>
       <c r="B33" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4368,7 +4368,7 @@
         <v>130270397</v>
       </c>
       <c r="B34" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>130270401</v>
       </c>
       <c r="B35" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>130270384</v>
       </c>
       <c r="B36" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130270403</v>
       </c>
       <c r="B37" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>130270404</v>
       </c>
       <c r="B38" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>130270400</v>
       </c>
       <c r="B39" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>130270386</v>
       </c>
       <c r="B40" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>130270387</v>
       </c>
       <c r="B41" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>130270385</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130270413</v>
       </c>
       <c r="B43" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5466,7 +5466,7 @@
         <v>130270412</v>
       </c>
       <c r="B44" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5581,7 +5581,7 @@
         <v>130270405</v>
       </c>
       <c r="B45" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>130270393</v>
       </c>
       <c r="B46" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>130270410</v>
       </c>
       <c r="B47" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5926,7 +5926,7 @@
         <v>130270391</v>
       </c>
       <c r="B48" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6138,7 +6138,7 @@
         <v>130270390</v>
       </c>
       <c r="B50" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>130270411</v>
       </c>
       <c r="B51" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 61292-2025 artfynd.xlsx
+++ b/artfynd/A 61292-2025 artfynd.xlsx
@@ -6038,45 +6038,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130270417</v>
+        <v>130270390</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>98970</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691737</v>
+        <v>691652</v>
       </c>
       <c r="R49" t="n">
-        <v>6612549</v>
+        <v>6612519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6111,12 +6123,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>16 st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6135,7 +6153,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130270390</v>
+        <v>130270411</v>
       </c>
       <c r="B50" t="n">
         <v>98970</v>
@@ -6165,7 +6183,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6182,10 +6200,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691652</v>
+        <v>691810</v>
       </c>
       <c r="R50" t="n">
-        <v>6612519</v>
+        <v>6612613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,7 +6240,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>16 st bladrosetter</t>
+          <t>5 st bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,57 +6268,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130270411</v>
+        <v>130270417</v>
       </c>
       <c r="B51" t="n">
-        <v>98970</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Riala-Sättra, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691810</v>
+        <v>691737</v>
       </c>
       <c r="R51" t="n">
-        <v>6612613</v>
+        <v>6612549</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6335,18 +6341,12 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>5 st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
